--- a/translations.xlsx
+++ b/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -101,6 +101,33 @@
 启用后，升级后剩余经验值将除以2。
 禁用后，所有经验值将被完全保留。
 需要重启游戏才能生效。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toggle02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable Optimization (Experimental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最適化を有効化（実験的）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用优化（实验性）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tooltip02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When enabled, extra levels from massive EXP gains are optimized and processed differently from vanilla behavior.
+This can significantly reduce lag when gaining very large EXP amounts, but some leftover EXP will be lost during processing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有効にすると、大量の経験値を一度に獲得した際に、追加のレベルアップ処理が最適化され、バニラとは異なる挙動になります。
+ラグを大幅に軽減できますが、一部の残り経験値が処理中に失われる場合があります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用后，大量经验一次性获取时会使用优化的升级处理方式，与原版行为不同。
+可以显著减少卡顿，不过在此过程中可能会损失少量剩余经验值。</t>
   </si>
 </sst>
 </file>
@@ -110,7 +137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -137,6 +164,11 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,7 +213,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -195,6 +227,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,8 +357,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="65.95"/>
@@ -415,6 +451,34 @@
         <v>23</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -118,16 +118,16 @@
     <t xml:space="preserve">tooltip02</t>
   </si>
   <si>
-    <t xml:space="preserve">When enabled, extra levels from massive EXP gains are optimized and processed differently from vanilla behavior.
-This can significantly reduce lag when gaining very large EXP amounts, but some leftover EXP will be lost during processing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有効にすると、大量の経験値を一度に獲得した際に、追加のレベルアップ処理が最適化され、バニラとは異なる挙動になります。
-ラグを大幅に軽減できますが、一部の残り経験値が処理中に失われる場合があります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用后，大量经验一次性获取时会使用优化的升级处理方式，与原版行为不同。
-可以显著减少卡顿，不过在此过程中可能会损失少量剩余经验值。</t>
+    <t xml:space="preserve">When enabled, large EXP gains are processed using an optimized batch-leveling method.
+This produces results close to leveling one step at a time while greatly reducing lag during massive EXP gains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有効にすると、大量の経験値獲得を段階的に処理する最適化方式が適用されます。
+手動で1レベルずつ上げる場合に近い結果となり、処理の重さを大幅に軽減できます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用后，大量经验将按逐级最佳方式进行优化处理。
+结果接近手动逐级升级，并可显著减轻卡顿。</t>
   </si>
 </sst>
 </file>
@@ -169,6 +169,7 @@
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
